--- a/AAII_Financials/Yearly/SLDP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SLDP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>SLDP</t>
   </si>
@@ -952,10 +952,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>1300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1153,10 +1153,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5800</v>
+        <v>5200</v>
       </c>
       <c r="E20" s="3">
-        <v>7600</v>
+        <v>4900</v>
       </c>
       <c r="F20" s="3">
         <v>-4900</v>
@@ -1195,10 +1195,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-87400</v>
+        <v>-86900</v>
       </c>
       <c r="E21" s="3">
-        <v>-96500</v>
+        <v>-93800</v>
       </c>
       <c r="F21" s="3">
         <v>-73800</v>
@@ -1657,10 +1657,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5800</v>
+        <v>-5200</v>
       </c>
       <c r="E32" s="3">
-        <v>-7600</v>
+        <v>-4900</v>
       </c>
       <c r="F32" s="3">
         <v>4900</v>
